--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
@@ -456,7 +456,7 @@
         <v>68.13224939828254</v>
       </c>
       <c r="C6">
-        <v>93.32684272659071</v>
+        <v>93.32684272659068</v>
       </c>
       <c r="D6">
         <v>103.2869828730602</v>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>357.5087543888388</v>
+        <v>357.5087543888387</v>
       </c>
       <c r="C8">
         <v>498.6223757263424</v>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>88.57554499379933</v>
+        <v>3.390451483016242</v>
       </c>
       <c r="C2">
-        <v>123.6189408115317</v>
+        <v>10.05512915691884</v>
       </c>
       <c r="D2">
-        <v>142.6917440762746</v>
+        <v>22.53027538046441</v>
       </c>
       <c r="E2">
-        <v>155.3902138438933</v>
+        <v>37.35341678939744</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>110.0413097136072</v>
+        <v>36.83015263883996</v>
       </c>
       <c r="C3">
-        <v>152.6961637409976</v>
+        <v>94.34884914077901</v>
       </c>
       <c r="D3">
-        <v>172.588039479098</v>
+        <v>129.6171398536899</v>
       </c>
       <c r="E3">
-        <v>187.5057914326663</v>
+        <v>156.2548261938886</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>89.88959294295074</v>
+        <v>3.413528845934838</v>
       </c>
       <c r="C4">
-        <v>127.6994382095966</v>
+        <v>9.121388443542614</v>
       </c>
       <c r="D4">
-        <v>149.2252560928734</v>
+        <v>17.00034563083367</v>
       </c>
       <c r="E4">
-        <v>166.9041835482289</v>
+        <v>24.54473287473954</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>78.20823992444279</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>107.5546739317773</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>117.9853275631305</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>127.0799969476143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.13224939828254</v>
+        <v>22.86956623159134</v>
       </c>
       <c r="C6">
-        <v>93.32684272659068</v>
+        <v>39.81075109316107</v>
       </c>
       <c r="D6">
-        <v>103.2869828730602</v>
+        <v>40.44804923700261</v>
       </c>
       <c r="E6">
-        <v>110.2448819789014</v>
+        <v>35.71313078189765</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.500689620578088</v>
+        <v>2.500229873526029</v>
       </c>
       <c r="C7">
-        <v>10.19165665066588</v>
+        <v>6.794437767110587</v>
       </c>
       <c r="D7">
-        <v>11.30057310237215</v>
+        <v>8.287086941739577</v>
       </c>
       <c r="E7">
-        <v>11.90686587437852</v>
+        <v>9.525492699502813</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>357.5087543888387</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>498.6223757263424</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>570.2055557300474</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>607.5443106949087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>103.8176863823793</v>
+        <v>186.468660007186</v>
       </c>
       <c r="C9">
-        <v>142.046561702182</v>
+        <v>406.9256574366858</v>
       </c>
       <c r="D9">
-        <v>156.672731131525</v>
+        <v>609.958885279044</v>
       </c>
       <c r="E9">
-        <v>165.7721082886922</v>
+        <v>792.8231265980932</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.09870525976798</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>59.77999993856822</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>66.24199612605035</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>68.15378775929922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>8.21680987508913</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>10.32116948848634</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>11.30215317346981</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.55506788507774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.72333084311544</v>
+        <v>229.9609095859563</v>
       </c>
       <c r="C12">
-        <v>24.96440692415187</v>
+        <v>333.2748324374275</v>
       </c>
       <c r="D12">
-        <v>26.45831461349329</v>
+        <v>298.9789551324741</v>
       </c>
       <c r="E12">
-        <v>26.40479109669189</v>
+        <v>230.1956146891088</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>25.28708665714868</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>33.17777014910926</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>37.04132603860492</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>38.53800064964739</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.390451483016242</v>
+        <v>11.4564776758447</v>
       </c>
       <c r="C2">
-        <v>10.05512915691884</v>
+        <v>15.98903665586278</v>
       </c>
       <c r="D2">
-        <v>22.53027538046441</v>
+        <v>18.45593815597324</v>
       </c>
       <c r="E2">
-        <v>37.35341678939744</v>
+        <v>20.09837496424009</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>36.83015263883996</v>
+        <v>69.81235840282821</v>
       </c>
       <c r="C3">
-        <v>94.34884914077901</v>
+        <v>96.87343178273065</v>
       </c>
       <c r="D3">
-        <v>129.6171398536899</v>
+        <v>109.4932266756396</v>
       </c>
       <c r="E3">
-        <v>156.2548261938886</v>
+        <v>118.9573401858973</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.413528845934838</v>
+        <v>8.326614925241756</v>
       </c>
       <c r="C4">
-        <v>9.121388443542614</v>
+        <v>11.82900059204684</v>
       </c>
       <c r="D4">
-        <v>17.00034563083367</v>
+        <v>13.82297109070827</v>
       </c>
       <c r="E4">
-        <v>24.54473287473954</v>
+        <v>15.46059805499384</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22.86956623159134</v>
+        <v>25.17671562703612</v>
       </c>
       <c r="C6">
-        <v>39.81075109316107</v>
+        <v>34.48680177812722</v>
       </c>
       <c r="D6">
-        <v>40.44804923700261</v>
+        <v>38.16734393382789</v>
       </c>
       <c r="E6">
-        <v>35.71313078189765</v>
+        <v>40.73847652810544</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.500229873526029</v>
+        <v>4.750436759699455</v>
       </c>
       <c r="C7">
-        <v>6.794437767110587</v>
+        <v>6.454715878755057</v>
       </c>
       <c r="D7">
-        <v>8.287086941739577</v>
+        <v>7.157029631502359</v>
       </c>
       <c r="E7">
-        <v>9.525492699502813</v>
+        <v>7.541015053773062</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>186.468660007186</v>
+        <v>346.2684333940131</v>
       </c>
       <c r="C9">
-        <v>406.9256574366858</v>
+        <v>473.7751543456558</v>
       </c>
       <c r="D9">
-        <v>609.958885279044</v>
+        <v>522.5585644883189</v>
       </c>
       <c r="E9">
-        <v>792.8231265980932</v>
+        <v>552.9081820040524</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>229.9609095859563</v>
+        <v>213.8962795685024</v>
       </c>
       <c r="C12">
-        <v>333.2748324374275</v>
+        <v>285.1946487221148</v>
       </c>
       <c r="D12">
-        <v>298.9789551324741</v>
+        <v>302.2611258060469</v>
       </c>
       <c r="E12">
-        <v>230.1956146891088</v>
+        <v>301.6496704400562</v>
       </c>
     </row>
     <row r="13" spans="1:5">
